--- a/products_master.xlsx
+++ b/products_master.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hemcorporation-my.sharepoint.com/personal/analytics_hemcorporation_onmicrosoft_com/Documents/Exports Product Catalogue Project/CatalogueMaker/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aeea0f31faf7c20a/Documents/GitHub/hem-catalogue-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="8_{BF88D132-6630-4A0D-8E96-78064D2F386C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49F51547-B16A-4CB7-8FBF-FDCBEAB8E00E}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{BF88D132-6630-4A0D-8E96-78064D2F386C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67C770AA-A873-4CFD-9C33-D076A5C2203B}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="19386" windowHeight="11466" xr2:uid="{8D633E80-C183-4D27-B044-EA23F7EF2B4F}"/>
   </bookViews>
@@ -170,9 +170,6 @@
     <t>Alpine Flowers</t>
   </si>
   <si>
-    <t>Sakura Blossom</t>
-  </si>
-  <si>
     <t>HEM-INC-JP01</t>
   </si>
   <si>
@@ -195,6 +192,9 @@
   </si>
   <si>
     <t>The best 2 of Hem</t>
+  </si>
+  <si>
+    <t>Jasmine Blossom</t>
   </si>
 </sst>
 </file>
@@ -815,16 +815,16 @@
         <v>13</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>30</v>
@@ -833,7 +833,7 @@
         <v>19</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="26.35" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -844,10 +844,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>8</v>
@@ -870,10 +870,10 @@
         <v>4</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
